--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>390.27</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8548.299999999999</v>
+        <v>8458.780000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>285.35</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8632.1</v>
+        <v>8535.93</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2921.02</v>
+        <v>2971.44</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37405.25</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11182.86</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9529.26</v>
+        <v>9514.49</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56451.91</v>
+        <v>56850.33</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>134801.34</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9795.129999999999</v>
+        <v>9754.059999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38202.81</v>
+        <v>38172.1</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>349.59</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15554.73</v>
+        <v>15745.89</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>55116.67</v>
+        <v>55794.06</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>134801.34</v>
+        <v>135538.53</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>11042.74</v>
+        <v>10883.61</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10939.36</v>
+        <v>10939.43</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>39594.3</v>
+        <v>39649.27</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>358.43</v>
+        <v>356.54</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13971.13</v>
+        <v>14183.82</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>58561.07</v>
+        <v>60336.82</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>126737.2</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>29001.65</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11323.87</v>
+        <v>11426.87</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12508.78</v>
+        <v>12620.2</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>20884.38</v>
+        <v>20803.77</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>61658.5</v>
+        <v>61977.73</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>483.57</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10430.07</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>161622.89</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12688.63</v>
+        <v>12887.39</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1373.79</v>
+        <v>1367.87</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>38466.05</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18796.29</v>
+        <v>18524.36</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>55519.05</v>
+        <v>54324.56</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>640.87</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2414.34</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2740.83</v>
+        <v>2677.06</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10569.55</v>
+        <v>10361.1</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>140394.38</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>13460.77</v>
+        <v>13438.26</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5535.67</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>19047.64</v>
+        <v>19126.59</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>38980.44</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>60850.44</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9663.59</v>
+        <v>9622.07</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>140680.11</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2619.57</v>
+        <v>2612.96</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>708.6799999999999</v>
+        <v>706.89</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12540.46</v>
+        <v>12633.88</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5664.2</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>38991.22</v>
+        <v>38902.72</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>19052.91</v>
+        <v>19005.86</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>57510.91</v>
+        <v>57693.96</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10270.4</v>
+        <v>10303.09</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>153341.65</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>14074.08</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5067.88</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>664.17</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>19803.34</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38743.2</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>65041.59</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>151187.37</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5239.75</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9902.68</v>
+        <v>9941.23</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14156.85</v>
+        <v>14189.31</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>161.12</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>595.02</v>
+        <v>593.83</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>306.13</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>37595.2</v>
+        <v>36992.41</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>19216.54</v>
+        <v>18992.94</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1628.47</v>
+        <v>1620.47</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>64998.18</v>
+        <v>65433.24</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1552-5221-CM25</t>
+          <t>1552-4601-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>388.27</v>
+        <v>32936.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1556-286-CM25</t>
+          <t>1552-4664-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8458.780000000001</v>
+        <v>1297.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2859-1529-CM25</t>
+          <t>5349-800-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>283.79</v>
+        <v>52037.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1558-302-CM25</t>
+          <t>1554-1127-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8535.93</v>
+        <v>121694.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1353-59-CM25</t>
+          <t>5349-2314-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.002.009-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2971.44</v>
+        <v>59862.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1552-5275-CM25</t>
+          <t>1552-5221-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>37338.91</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1557-418-CM25</t>
+          <t>1556-286-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11163.03</v>
+        <v>8458.780000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1556-305-CM25</t>
+          <t>2859-1529-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9514.49</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5349-2472-CM25</t>
+          <t>1558-302-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>56850.33</v>
+        <v>8535.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1554-1974-CM25</t>
+          <t>1353-59-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.002.009-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>133460.13</v>
+        <v>2971.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1558-337-CM25</t>
+          <t>1552-5275-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9754.059999999999</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1552-5305-CM25</t>
+          <t>1557-418-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>38172.1</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2609-87-CM25</t>
+          <t>1556-305-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>350.04</v>
+        <v>9514.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1557-455-CM25</t>
+          <t>5349-2472-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15745.89</v>
+        <v>56850.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5349-2718-CM25</t>
+          <t>1554-1974-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>55794.06</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1554-2118-CM25</t>
+          <t>1558-337-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>135538.53</v>
+        <v>9754.059999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1556-6-CM26</t>
+          <t>1552-5305-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>10883.61</v>
+        <v>38172.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1558-10-CM26</t>
+          <t>2609-87-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>Departamento Provincial de Educación Copiapo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10939.43</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1552-19-CM26</t>
+          <t>1557-455-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>39649.27</v>
+        <v>15745.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1558-12-CM26</t>
+          <t>5349-2718-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>356.54</v>
+        <v>55794.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1557-13-CM26</t>
+          <t>1554-2118-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>14183.82</v>
+        <v>135538.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5349-197-CM26</t>
+          <t>1556-6-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>60336.82</v>
+        <v>10883.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1554-167-CM26</t>
+          <t>1558-10-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>127104.35</v>
+        <v>10939.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1552-58-CM26</t>
+          <t>1552-19-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>28879.37</v>
+        <v>39649.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1556-39-CM26</t>
+          <t>1558-12-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>11426.87</v>
+        <v>356.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1558-62-CM26</t>
+          <t>1557-13-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>12620.2</v>
+        <v>14183.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1557-48-CM26</t>
+          <t>5349-197-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>20803.77</v>
+        <v>60336.82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5349-427-CM26</t>
+          <t>1554-167-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>61977.73</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>651-35-CM26</t>
+          <t>1552-58-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>491.54</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1556-65-CM26</t>
+          <t>1556-39-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10601.97</v>
+        <v>11426.87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1554-320-CM26</t>
+          <t>1558-62-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>164286.67</v>
+        <v>12620.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1558-96-CM26</t>
+          <t>1557-48-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12887.39</v>
+        <v>20803.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2859-126-CM26</t>
+          <t>5349-427-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1367.87</v>
+        <v>61977.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1552-114-CM26</t>
+          <t>651-35-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>38300.34</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1557-93-CM26</t>
+          <t>1556-65-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>18524.36</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5349-614-CM26</t>
+          <t>1554-320-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>54324.56</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1373324-29-CM26</t>
+          <t>1558-96-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>625.96</v>
+        <v>12887.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>707416-25-CM26</t>
+          <t>2859-126-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2358.16</v>
+        <v>1367.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1373324-28-CM26</t>
+          <t>1552-114-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2677.06</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1556-93-CM26</t>
+          <t>1557-93-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>10361.1</v>
+        <v>18524.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1554-623-CM26</t>
+          <t>5349-614-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>136697.33</v>
+        <v>54324.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1558-125-CM26</t>
+          <t>707416-25-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>13438.26</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>707416-30-CM26</t>
+          <t>1373324-28-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5607.91</v>
+        <v>2677.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1557-130-CM26</t>
+          <t>1373324-29-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>19126.59</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1552-169-CM26</t>
+          <t>1556-93-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>39061.19</v>
+        <v>10361.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5349-860-CM26</t>
+          <t>1554-623-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>60976.5</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1556-116-CM26</t>
+          <t>1558-125-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9622.07</v>
+        <v>13438.26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1554-785-CM26</t>
+          <t>707416-30-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>138767.48</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1373324-39-CM26</t>
+          <t>1557-130-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2612.96</v>
+        <v>19126.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1373324-40-CM26</t>
+          <t>5349-860-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3513,27 +3513,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>706.89</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1558-162-CM26</t>
+          <t>1552-169-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12633.88</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>707416-41-CM26</t>
+          <t>1556-116-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5706.4</v>
+        <v>9622.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1552-214-CM26</t>
+          <t>1554-785-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>38902.72</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1557-170-CM26</t>
+          <t>1373324-39-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>19005.86</v>
+        <v>2612.96</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5349-1096-CM26</t>
+          <t>1373324-40-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>57693.96</v>
+        <v>706.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1556-149-CM26</t>
+          <t>1558-162-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10303.09</v>
+        <v>12633.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1554-964-CM26</t>
+          <t>707416-41-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>155935.02</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1558-201-CM26</t>
+          <t>1552-214-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>13880.7</v>
+        <v>38902.72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>707416-51-CM26</t>
+          <t>1557-170-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,28 +4107,28 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4998.24</v>
+        <v>19005.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2859-586-CM26</t>
+          <t>5349-1096-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4168,28 +4168,28 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>666.22</v>
+        <v>57693.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1557-226-CM26</t>
+          <t>1556-149-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,18 +4229,18 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>19750.96</v>
+        <v>10303.09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1552-311-CM26</t>
+          <t>1554-964-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,18 +4290,18 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38227.13</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5349-1302-CM26</t>
+          <t>1558-201-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,28 +4351,28 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>63704.87</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1554-1114-CM26</t>
+          <t>707416-51-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>152707.94</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>707416-63-CM26</t>
+          <t>2859-586-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5292.22</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1556-186-CM26</t>
+          <t>1557-226-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9941.23</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1558-253-CM26</t>
+          <t>1552-311-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>14189.31</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1376-473-CM26</t>
+          <t>5349-1302-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>162.25</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2609-31-CM26</t>
+          <t>1554-1114-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>593.83</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1079486-155-CM26</t>
+          <t>707416-63-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>305.52</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1552-386-CM26</t>
+          <t>1556-186-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>36992.41</v>
+        <v>9941.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1557-260-CM26</t>
+          <t>1558-253-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>18992.94</v>
+        <v>14189.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3281-60-CM26</t>
+          <t>1376-473-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>Dirección Regional de Gendarmeria - Copiapo</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1620.47</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5349-1486-CM26</t>
+          <t>2609-31-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>Departamento Provincial de Educación Copiapo</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,6 +5022,311 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
+        <v>593.83</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1079486-155-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>60.505.105-7</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS III ZONA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>305.52</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1552-386-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>36992.41</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1557-260-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>18992.94</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3281-60-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1620.47</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>5349-1486-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
         <v>65433.24</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1552-4601-CM25</t>
+          <t>1552-4611-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>32936.43</v>
+        <v>1243.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1552-4611-CM25</t>
+          <t>5349-320-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1243.85</v>
+        <v>50908.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5349-320-CM25</t>
+          <t>1557-44-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>50908.4</v>
+        <v>9575.940000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1557-44-CM25</t>
+          <t>1554-210-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9575.940000000001</v>
+        <v>122705.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1554-210-CM25</t>
+          <t>1373324-25-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>122705.45</v>
+        <v>948.9299999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1373324-25-CM25</t>
+          <t>1373324-24-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>948.9299999999999</v>
+        <v>270.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1373324-24-CM25</t>
+          <t>1373324-23-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>270.05</v>
+        <v>2907.09</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1373324-23-CM25</t>
+          <t>1556-20-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2907.09</v>
+        <v>8656.280000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1556-20-CM25</t>
+          <t>1558-35-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8656.280000000001</v>
+        <v>7886.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1558-35-CM25</t>
+          <t>651-38-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7886.77</v>
+        <v>464.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>651-38-CM25</t>
+          <t>1552-4645-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,22 +1444,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>464.56</v>
+        <v>23114.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1552-4645-CM25</t>
+          <t>1557-76-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>23114.59</v>
+        <v>18101.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1557-76-CM25</t>
+          <t>5349-459-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18101.94</v>
+        <v>49468.46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5349-459-CM25</t>
+          <t>1554-420-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>49468.46</v>
+        <v>115222.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1554-420-CM25</t>
+          <t>1552-4664-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>115222.8</v>
+        <v>1297.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1552-4664-CM25</t>
+          <t>1556-43-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1297.54</v>
+        <v>8399.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1556-43-CM25</t>
+          <t>550999-5-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8399.17</v>
+        <v>9389.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>550999-5-CM25</t>
+          <t>550999-6-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9389.98</v>
+        <v>272.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>550999-6-CM25</t>
+          <t>1558-54-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>272.31</v>
+        <v>7944.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1558-54-CM25</t>
+          <t>949-12-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>60.901.005-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7944.79</v>
+        <v>3807.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>949-12-CM25</t>
+          <t>707416-19-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.901.005-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3807.87</v>
+        <v>2142.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707416-19-CM25</t>
+          <t>1552-4716-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2142.39</v>
+        <v>45776.28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1552-4716-CM25</t>
+          <t>1557-102-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>45776.28</v>
+        <v>18588.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1557-102-CM25</t>
+          <t>5349-597-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>18588.57</v>
+        <v>49093.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5349-597-CM25</t>
+          <t>1554-666-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>49093.94</v>
+        <v>115620.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1554-666-CM25</t>
+          <t>1556-70-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>115620.69</v>
+        <v>8311.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1556-70-CM25</t>
+          <t>1552-4737-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8311.41</v>
+        <v>1261.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1552-4737-CM25</t>
+          <t>1558-96-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1261.71</v>
+        <v>7924.07</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1558-96-CM25</t>
+          <t>751-129-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7924.07</v>
+        <v>2991.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>751-129-CM25</t>
+          <t>1554-806-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2603,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2991.97</v>
+        <v>10027.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1554-806-CM25</t>
+          <t>1552-4774-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10027.94</v>
+        <v>26657.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1552-4774-CM25</t>
+          <t>1557-130-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>26657.85</v>
+        <v>18233.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1557-130-CM25</t>
+          <t>5349-800-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18233.97</v>
+        <v>52037.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5349-800-CM25</t>
+          <t>5349-813-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>52037.48</v>
+        <v>3283.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5349-813-CM25</t>
+          <t>1552-4785-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3283.54</v>
+        <v>1308.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1552-4785-CM25</t>
+          <t>1554-908-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1308.47</v>
+        <v>128110.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1554-908-CM25</t>
+          <t>2609-16-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>128110.42</v>
+        <v>422.46</v>
       </c>
     </row>
     <row r="44">
@@ -3137,7 +3137,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2609-16-CM25</t>
+          <t>1558-122-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>422.46</v>
+        <v>8856.049999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1558-122-CM25</t>
+          <t>2859-454-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8856.049999999999</v>
+        <v>1330.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2859-454-CM25</t>
+          <t>2609-23-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1330.59</v>
+        <v>264.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2609-23-CM25</t>
+          <t>1028871-967-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>264.31</v>
+        <v>3513.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1028871-967-CM25</t>
+          <t>1557-174-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3513.88</v>
+        <v>18232.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1557-174-CM25</t>
+          <t>1552-4845-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18232.2</v>
+        <v>35183.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1552-4845-CM25</t>
+          <t>5349-977-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>35183.86</v>
+        <v>53242.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5349-977-CM25</t>
+          <t>1552-4861-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>53242.62</v>
+        <v>1310.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1552-4861-CM25</t>
+          <t>1554-1127-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1310.28</v>
+        <v>121694.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1554-1127-CM25</t>
+          <t>1556-111-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>121694.38</v>
+        <v>9237.209999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1556-111-CM25</t>
+          <t>1558-152-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9237.209999999999</v>
+        <v>8661.219999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1558-152-CM25</t>
+          <t>1197-151-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8661.219999999999</v>
+        <v>373.79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1197-151-CM25</t>
+          <t>1197-150-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>373.79</v>
+        <v>1174.76</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1197-148-CM25</t>
+          <t>1197-149-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>640.78</v>
+        <v>2135.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1197-149-CM25</t>
+          <t>1197-148-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2135.93</v>
+        <v>640.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1197-150-CM25</t>
+          <t>233-40-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1174.76</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>233-40-CM25</t>
+          <t>233-41-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>331.09</v>
+        <v>662.1900000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>233-41-CM25</t>
+          <t>1552-4894-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>662.1900000000001</v>
+        <v>29468.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1552-4894-CM25</t>
+          <t>5349-1156-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>29468.72</v>
+        <v>55317.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5349-1156-CM25</t>
+          <t>1557-210-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>55317.21</v>
+        <v>18274.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1557-210-CM25</t>
+          <t>1552-4929-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>18274.87</v>
+        <v>1326.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1552-4929-CM25</t>
+          <t>1554-1271-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1326.91</v>
+        <v>135178.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1554-1271-CM25</t>
+          <t>1556-147-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>135178.96</v>
+        <v>9430.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1556-147-CM25</t>
+          <t>1558-178-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9430.5</v>
+        <v>9494.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1558-178-CM25</t>
+          <t>1556-150-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9494.4</v>
+        <v>592.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1556-150-CM25</t>
+          <t>1373324-82-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>592.7</v>
+        <v>536.47</v>
       </c>
     </row>
     <row r="71">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1373324-82-CM25</t>
+          <t>1557-230-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>536.47</v>
+        <v>10924.57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1557-230-CM25</t>
+          <t>1552-4965-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>10924.57</v>
+        <v>36091.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1552-4965-CM25</t>
+          <t>5349-1500-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>36091.78</v>
+        <v>56308.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5349-1500-CM25</t>
+          <t>1556-168-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>56308.09</v>
+        <v>10449.19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1556-168-CM25</t>
+          <t>1552-4973-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10449.19</v>
+        <v>1272.58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1552-4973-CM25</t>
+          <t>1554-1426-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1272.58</v>
+        <v>131542.71</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1554-1426-CM25</t>
+          <t>1558-209-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>131542.71</v>
+        <v>8240.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1558-209-CM25</t>
+          <t>1552-5033-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8240.6</v>
+        <v>34285.36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1552-5033-CM25</t>
+          <t>1557-285-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>34285.36</v>
+        <v>10843.18</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1557-285-CM25</t>
+          <t>2035-91-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10843.18</v>
+        <v>908.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2035-91-CM25</t>
+          <t>5349-1739-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5414,17 +5414,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>908.49</v>
+        <v>53097.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5349-1739-CM25</t>
+          <t>1554-1556-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>53097.39</v>
+        <v>131519.93</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1554-1556-CM25</t>
+          <t>707416-89-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>131519.93</v>
+        <v>2357.63</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>707416-89-CM25</t>
+          <t>1556-210-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2357.63</v>
+        <v>9197.389999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1556-210-CM25</t>
+          <t>1552-5057-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9197.389999999999</v>
+        <v>1276.41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1552-5057-CM25</t>
+          <t>1558-249-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1276.41</v>
+        <v>8836.4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1558-249-CM25</t>
+          <t>5349-1879-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8836.4</v>
+        <v>52993.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5349-1879-CM25</t>
+          <t>1552-5105-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>52993.93</v>
+        <v>1291.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1552-5105-CM25</t>
+          <t>1552-5103-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1291.6</v>
+        <v>34618.77</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1552-5103-CM25</t>
+          <t>1557-319-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>34618.77</v>
+        <v>10940.56</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1557-319-CM25</t>
+          <t>1556-248-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>10940.56</v>
+        <v>8321.15</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1556-248-CM25</t>
+          <t>1554-1672-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>8321.15</v>
+        <v>128326.35</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1554-1672-CM25</t>
+          <t>2609-68-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>128326.35</v>
+        <v>329.17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2609-68-CM25</t>
+          <t>1558-276-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>329.17</v>
+        <v>9109.379999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1558-276-CM25</t>
+          <t>1552-5181-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>9109.379999999999</v>
+        <v>36824.28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1552-5181-CM25</t>
+          <t>1557-365-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>36824.28</v>
+        <v>11090.73</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1557-365-CM25</t>
+          <t>5349-2314-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11090.73</v>
+        <v>59862.45</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5349-2314-CM25</t>
+          <t>1554-1809-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>59862.45</v>
+        <v>131155.55</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1554-1809-CM25</t>
+          <t>1552-5221-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>131155.55</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1552-5221-CM25</t>
+          <t>1556-286-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>388.27</v>
+        <v>8458.780000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1556-286-CM25</t>
+          <t>2859-1529-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8458.780000000001</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2859-1529-CM25</t>
+          <t>1558-302-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>283.79</v>
+        <v>8535.93</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1558-302-CM25</t>
+          <t>1353-59-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.002.009-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8535.93</v>
+        <v>2971.44</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1353-59-CM25</t>
+          <t>1552-5275-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.002.009-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2971.44</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1552-5275-CM25</t>
+          <t>1557-418-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>37338.91</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1557-418-CM25</t>
+          <t>1556-305-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>11163.03</v>
+        <v>9514.49</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1556-305-CM25</t>
+          <t>5349-2472-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>9514.49</v>
+        <v>56850.33</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5349-2472-CM25</t>
+          <t>1554-1974-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>56850.33</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1554-1974-CM25</t>
+          <t>1558-337-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,22 +7117,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>133460.13</v>
+        <v>9754.059999999999</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1558-337-CM25</t>
+          <t>1552-5305-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>9754.059999999999</v>
+        <v>38172.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1552-5305-CM25</t>
+          <t>2609-87-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>38172.1</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2609-87-CM25</t>
+          <t>5349-2718-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>350.04</v>
+        <v>55794.06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5349-2718-CM25</t>
+          <t>1557-455-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>55794.06</v>
+        <v>15745.89</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1557-455-CM25</t>
+          <t>1554-2118-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>15745.89</v>
+        <v>135538.53</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1554-2118-CM25</t>
+          <t>1556-6-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>135538.53</v>
+        <v>10883.61</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1556-6-CM26</t>
+          <t>1558-10-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10883.61</v>
+        <v>10939.43</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1558-10-CM26</t>
+          <t>1552-19-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>10939.43</v>
+        <v>39649.27</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1552-19-CM26</t>
+          <t>1558-12-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +7666,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>39649.27</v>
+        <v>356.54</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1558-12-CM26</t>
+          <t>1557-13-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>356.54</v>
+        <v>14183.82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1557-13-CM26</t>
+          <t>5349-197-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>14183.82</v>
+        <v>60336.82</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5349-197-CM26</t>
+          <t>1554-167-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>60336.82</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1554-167-CM26</t>
+          <t>1552-58-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>127104.35</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1552-58-CM26</t>
+          <t>1556-39-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>28879.37</v>
+        <v>11426.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1556-39-CM26</t>
+          <t>1558-62-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>11426.87</v>
+        <v>12620.2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1558-62-CM26</t>
+          <t>1557-48-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>12620.2</v>
+        <v>20803.77</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1557-48-CM26</t>
+          <t>5349-427-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>20803.77</v>
+        <v>61977.73</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5349-427-CM26</t>
+          <t>651-35-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8210,27 +8210,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>61977.73</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>651-35-CM26</t>
+          <t>1556-65-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>491.54</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1556-65-CM26</t>
+          <t>1554-320-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>10601.97</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1554-320-CM26</t>
+          <t>1558-96-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>164286.67</v>
+        <v>12887.39</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1558-96-CM26</t>
+          <t>2859-126-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>12887.39</v>
+        <v>1367.87</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2859-126-CM26</t>
+          <t>1552-114-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1367.87</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1552-114-CM26</t>
+          <t>1557-93-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>38300.34</v>
+        <v>18524.36</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1557-93-CM26</t>
+          <t>5349-614-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>18524.36</v>
+        <v>54324.56</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>5349-614-CM26</t>
+          <t>707416-25-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>54324.56</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>707416-25-CM26</t>
+          <t>1373324-28-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2358.16</v>
+        <v>2677.06</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1373324-28-CM26</t>
+          <t>1373324-29-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2677.06</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1373324-29-CM26</t>
+          <t>1556-93-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>625.96</v>
+        <v>10361.1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1556-93-CM26</t>
+          <t>1554-623-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>10361.1</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1554-623-CM26</t>
+          <t>1558-125-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>136697.33</v>
+        <v>13438.26</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1558-125-CM26</t>
+          <t>707416-30-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>13438.26</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>707416-30-CM26</t>
+          <t>1557-130-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5607.91</v>
+        <v>19126.59</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1557-130-CM26</t>
+          <t>1552-169-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>19126.59</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1552-169-CM26</t>
+          <t>5349-860-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>39061.19</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>5349-860-CM26</t>
+          <t>1556-116-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>60976.5</v>
+        <v>9622.07</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1556-116-CM26</t>
+          <t>1554-785-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9369,12 +9369,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>9622.07</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1554-785-CM26</t>
+          <t>1373324-40-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,22 +9435,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>138767.48</v>
+        <v>706.89</v>
       </c>
     </row>
     <row r="149">
@@ -9542,7 +9542,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1373324-40-CM26</t>
+          <t>1558-162-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,22 +9557,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>706.89</v>
+        <v>12633.88</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1558-162-CM26</t>
+          <t>707416-41-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>12633.88</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>707416-41-CM26</t>
+          <t>1552-214-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5706.4</v>
+        <v>38902.72</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1552-214-CM26</t>
+          <t>1557-170-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>38902.72</v>
+        <v>19005.86</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1557-170-CM26</t>
+          <t>1556-149-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>19005.86</v>
+        <v>10303.09</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1556-149-CM26</t>
+          <t>5349-1096-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>10303.09</v>
+        <v>57693.96</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>5349-1096-CM26</t>
+          <t>1554-964-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>57693.96</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1554-964-CM26</t>
+          <t>1558-201-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>155935.02</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1558-201-CM26</t>
+          <t>707416-51-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10085,18 +10085,18 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13880.7</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>707416-51-CM26</t>
+          <t>2859-586-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4998.24</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2859-586-CM26</t>
+          <t>1557-226-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>666.22</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1557-226-CM26</t>
+          <t>1552-311-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>19750.96</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1552-311-CM26</t>
+          <t>5349-1302-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>38227.13</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5349-1302-CM26</t>
+          <t>1554-1114-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>63704.87</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1554-1114-CM26</t>
+          <t>707416-63-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>152707.94</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>707416-63-CM26</t>
+          <t>1556-186-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5292.22</v>
+        <v>9941.23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1556-186-CM26</t>
+          <t>1558-253-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>9941.23</v>
+        <v>14189.31</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1558-253-CM26</t>
+          <t>1376-473-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>14189.31</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1376-473-CM26</t>
+          <t>2609-31-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>162.25</v>
+        <v>593.83</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2609-31-CM26</t>
+          <t>1079486-155-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>593.83</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1079486-155-CM26</t>
+          <t>1552-386-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10777,22 +10777,22 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>305.52</v>
+        <v>36992.41</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1552-386-CM26</t>
+          <t>1557-260-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,22 +10838,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>36992.41</v>
+        <v>18992.94</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1557-260-CM26</t>
+          <t>3281-60-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,22 +10899,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>18992.94</v>
+        <v>1620.47</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3281-60-CM26</t>
+          <t>5349-1486-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1620.47</v>
+        <v>65433.24</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5349-1486-CM26</t>
+          <t>1556-215-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>65433.24</v>
+        <v>10338.76</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1556-215-CM26</t>
+          <t>1028871-438-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>10338.76</v>
+        <v>9816.030000000001</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1028871-438-CM26</t>
+          <t>1028871-439-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>9816.030000000001</v>
+        <v>2502.32</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1028871-439-CM26</t>
+          <t>1554-1309-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2502.32</v>
+        <v>147852.81</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1554-1309-CM26</t>
+          <t>1558-300-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,22 +11265,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>147852.81</v>
+        <v>14110.8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1558-300-CM26</t>
+          <t>707416-68-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,22 +11326,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>14110.8</v>
+        <v>5259.83</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>707416-68-CM26</t>
+          <t>1373324-62-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5259.83</v>
+        <v>272.12</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1373324-62-CM26</t>
+          <t>1557-296-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>272.12</v>
+        <v>19377.64</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1557-296-CM26</t>
+          <t>1079486-190-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>19377.64</v>
+        <v>26809.85</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1079486-190-CM26</t>
+          <t>1552-424-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>26809.85</v>
+        <v>38401.19</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1552-424-CM26</t>
+          <t>5349-1763-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>38401.19</v>
+        <v>60473.35</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5349-1763-CM26</t>
+          <t>707416-73-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11687,27 +11687,27 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11732,7 +11732,495 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>60473.35</v>
+        <v>2344.84</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1554-1513-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>152580.19</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1556-241-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>61.606.305-7</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>10743.56</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1558-333-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.606.306-5</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>13971.31</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>707416-83-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>5733.05</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1552-473-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>61.606.300-6</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>36764.71</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1557-337-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>18525.25</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>5349-1956-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>60500.37</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1079486-227-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>60.505.105-7</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>16093.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1879,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>550999-5-CM25</t>
+          <t>550999-6-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9389.98</v>
+        <v>272.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>550999-6-CM25</t>
+          <t>550999-5-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>272.31</v>
+        <v>9389.98</v>
       </c>
     </row>
     <row r="25">
@@ -2594,7 +2594,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1558-96-CM25</t>
+          <t>751-129-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7924.07</v>
+        <v>2991.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>751-129-CM25</t>
+          <t>1558-96-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2991.97</v>
+        <v>7924.07</v>
       </c>
     </row>
     <row r="36">
@@ -3569,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1557-174-CM25</t>
+          <t>1552-4845-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>18232.2</v>
+        <v>35183.86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1552-4845-CM25</t>
+          <t>1557-174-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>35183.86</v>
+        <v>18232.2</v>
       </c>
     </row>
     <row r="51">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1554-1127-CM25</t>
+          <t>1556-111-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>121694.38</v>
+        <v>9237.209999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1556-111-CM25</t>
+          <t>1554-1127-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9237.209999999999</v>
+        <v>121694.38</v>
       </c>
     </row>
     <row r="55">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1197-150-CM25</t>
+          <t>1197-148-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1174.76</v>
+        <v>640.78</v>
       </c>
     </row>
     <row r="58">
@@ -4219,7 +4219,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1197-148-CM25</t>
+          <t>1197-150-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>640.78</v>
+        <v>1174.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>233-40-CM25</t>
+          <t>233-41-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>331.09</v>
+        <v>662.1900000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>233-41-CM25</t>
+          <t>233-40-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>662.1900000000001</v>
+        <v>331.09</v>
       </c>
     </row>
     <row r="62">
@@ -4609,7 +4609,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1552-4929-CM25</t>
+          <t>1554-1271-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1326.91</v>
+        <v>135178.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1554-1271-CM25</t>
+          <t>1552-4929-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>135178.96</v>
+        <v>1326.91</v>
       </c>
     </row>
     <row r="67">
@@ -4934,7 +4934,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1373324-82-CM25</t>
+          <t>1373324-83-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>536.47</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1373324-83-CM25</t>
+          <t>1373324-82-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>165.58</v>
+        <v>536.47</v>
       </c>
     </row>
     <row r="72">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2035-91-CM25</t>
+          <t>5349-1739-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>908.49</v>
+        <v>53097.39</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5349-1739-CM25</t>
+          <t>2035-91-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>53097.39</v>
+        <v>908.49</v>
       </c>
     </row>
     <row r="83">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5349-2314-CM25</t>
+          <t>1554-1809-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>59862.45</v>
+        <v>131155.55</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1554-1809-CM25</t>
+          <t>5349-2314-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>131155.55</v>
+        <v>59862.45</v>
       </c>
     </row>
     <row r="100">
@@ -7209,7 +7209,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1552-5275-CM25</t>
+          <t>1557-418-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>37338.91</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1557-418-CM25</t>
+          <t>1552-5275-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>11163.03</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="107">
@@ -8704,7 +8704,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>651-35-CM26</t>
+          <t>1556-65-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8724,17 +8724,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>491.54</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1556-65-CM26</t>
+          <t>651-35-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>10601.97</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="130">
@@ -9224,7 +9224,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>707416-25-CM26</t>
+          <t>1373324-29-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2358.16</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="137">
@@ -9354,7 +9354,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1373324-29-CM26</t>
+          <t>707416-25-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>625.96</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="139">
@@ -9744,7 +9744,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1552-169-CM26</t>
+          <t>5349-860-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>39061.19</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>5349-860-CM26</t>
+          <t>1552-169-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>60976.5</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="146">
@@ -10589,7 +10589,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1558-201-CM26</t>
+          <t>707416-51-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>13880.7</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>707416-51-CM26</t>
+          <t>1558-201-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>4998.24</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="159">
@@ -11824,7 +11824,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1028871-439-CM26</t>
+          <t>1554-1309-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2502.32</v>
+        <v>147852.81</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1554-1309-CM26</t>
+          <t>1028871-439-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>147852.81</v>
+        <v>2502.32</v>
       </c>
     </row>
     <row r="178">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1373324-62-CM26</t>
+          <t>1557-296-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>272.12</v>
+        <v>19377.64</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1557-296-CM26</t>
+          <t>1373324-62-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>19377.64</v>
+        <v>272.12</v>
       </c>
     </row>
     <row r="182">
@@ -12539,7 +12539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1556-241-CM26</t>
+          <t>1558-333-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>10743.56</v>
+        <v>13971.31</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1558-333-CM26</t>
+          <t>1556-241-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>13971.31</v>
+        <v>10743.56</v>
       </c>
     </row>
     <row r="189">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12989,6 +12989,656 @@
       </c>
       <c r="M193" s="2" t="n">
         <v>16093.4</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2859-1172-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>508.21</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2859-1174-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>508.21</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1554-1672-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.606.307-3</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>139198.99</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1556-274-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.606.305-7</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>10220.51</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1558-372-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.606.306-5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>12739.69</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1376-756-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.004.010-1</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>326.27</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>707416-97-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>5227.79</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2859-1288-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>489.4</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1028871-654-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>2416.09</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1557-378-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.606.309-k</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>18133.37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1552-4611-CM25</t>
+          <t>1552-4601-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-01-24</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1243.85</v>
+        <v>32936.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5349-320-CM25</t>
+          <t>1552-4611-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>50908.4</v>
+        <v>1243.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1557-44-CM25</t>
+          <t>5349-320-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9575.940000000001</v>
+        <v>50908.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1554-210-CM25</t>
+          <t>1557-44-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>122705.45</v>
+        <v>9575.940000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1373324-25-CM25</t>
+          <t>1554-210-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>948.9299999999999</v>
+        <v>122705.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1373324-24-CM25</t>
+          <t>1373324-25-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>270.05</v>
+        <v>948.9299999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1373324-23-CM25</t>
+          <t>1373324-24-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2907.09</v>
+        <v>270.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1373324-22-CM25</t>
+          <t>1373324-23-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>702.14</v>
+        <v>2907.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1556-20-CM25</t>
+          <t>1373324-22-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1309,22 +1309,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8656.280000000001</v>
+        <v>702.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1558-35-CM25</t>
+          <t>1556-20-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7886.77</v>
+        <v>8656.280000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>651-38-CM25</t>
+          <t>1558-35-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1439,22 +1439,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>464.56</v>
+        <v>7886.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1552-4645-CM25</t>
+          <t>651-38-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1504,22 +1504,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>23114.59</v>
+        <v>464.56</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1557-76-CM25</t>
+          <t>1552-4645-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-02-21</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18101.94</v>
+        <v>23114.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5349-459-CM25</t>
+          <t>1557-76-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>49468.46</v>
+        <v>18101.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1554-420-CM25</t>
+          <t>5349-459-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>115222.8</v>
+        <v>49468.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1552-4664-CM25</t>
+          <t>1554-420-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1297.54</v>
+        <v>115222.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1556-43-CM25</t>
+          <t>1552-4664-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8399.17</v>
+        <v>1297.54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>550999-6-CM25</t>
+          <t>1556-43-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.511.030-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>272.31</v>
+        <v>8399.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>550999-5-CM25</t>
+          <t>550999-6-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2003,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9389.98</v>
+        <v>272.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1558-54-CM25</t>
+          <t>550999-5-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>60.511.030-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7944.79</v>
+        <v>9389.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>949-12-CM25</t>
+          <t>1558-54-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.901.005-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3807.87</v>
+        <v>7944.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>707416-19-CM25</t>
+          <t>949-12-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.901.005-3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2142.39</v>
+        <v>3807.87</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1552-4716-CM25</t>
+          <t>707416-19-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>45776.28</v>
+        <v>2142.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1557-102-CM25</t>
+          <t>1552-4716-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>18588.57</v>
+        <v>45776.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5349-597-CM25</t>
+          <t>1557-102-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>49093.94</v>
+        <v>18588.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1554-666-CM25</t>
+          <t>5349-597-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>115620.69</v>
+        <v>49093.94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1556-70-CM25</t>
+          <t>1554-666-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8311.41</v>
+        <v>115620.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1552-4737-CM25</t>
+          <t>1556-70-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1261.71</v>
+        <v>8311.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>751-129-CM25</t>
+          <t>1552-4737-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2609,22 +2609,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>72.232.200-2</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2991.97</v>
+        <v>1261.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1558-96-CM25</t>
+          <t>751-129-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>72.232.200-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>GOBIERNO REGIONAL DE ATACAMA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7924.07</v>
+        <v>2991.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1554-806-CM25</t>
+          <t>1558-96-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10027.94</v>
+        <v>7924.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1552-4774-CM25</t>
+          <t>1554-806-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>26657.85</v>
+        <v>10027.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1557-130-CM25</t>
+          <t>1552-4774-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,13 +2913,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18233.97</v>
+        <v>26657.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5349-800-CM25</t>
+          <t>1557-130-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>52037.48</v>
+        <v>18233.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5349-813-CM25</t>
+          <t>5349-800-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3283.54</v>
+        <v>52037.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1552-4785-CM25</t>
+          <t>5349-813-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1308.47</v>
+        <v>3283.54</v>
       </c>
     </row>
     <row r="42">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2609-16-CM25</t>
+          <t>1552-4785-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>422.46</v>
+        <v>1308.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1556-86-CM25</t>
+          <t>2609-16-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7766.76</v>
+        <v>422.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1558-122-CM25</t>
+          <t>1556-86-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8856.049999999999</v>
+        <v>7766.76</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2859-454-CM25</t>
+          <t>1558-122-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1330.59</v>
+        <v>8856.049999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2609-23-CM25</t>
+          <t>2859-454-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>264.31</v>
+        <v>1330.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1028871-967-CM25</t>
+          <t>2609-23-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3513.88</v>
+        <v>264.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1552-4845-CM25</t>
+          <t>1028871-967-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>35183.86</v>
+        <v>3513.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1557-174-CM25</t>
+          <t>1552-4845-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18232.2</v>
+        <v>35183.86</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5349-977-CM25</t>
+          <t>1557-174-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>53242.62</v>
+        <v>18232.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1552-4861-CM25</t>
+          <t>5349-977-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1310.28</v>
+        <v>53242.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1556-111-CM25</t>
+          <t>1552-4861-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9237.209999999999</v>
+        <v>1310.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1554-1127-CM25</t>
+          <t>1556-111-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>121694.38</v>
+        <v>9237.209999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1558-152-CM25</t>
+          <t>1554-1127-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8661.219999999999</v>
+        <v>121694.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1197-151-CM25</t>
+          <t>1558-152-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>373.79</v>
+        <v>8661.219999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4284,7 +4284,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>233-41-CM25</t>
+          <t>1197-151-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.511.033-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>662.1900000000001</v>
+        <v>373.79</v>
       </c>
     </row>
     <row r="61">
@@ -4414,7 +4414,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1552-4894-CM25</t>
+          <t>233-41-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>60.511.033-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE HUASCO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>29468.72</v>
+        <v>662.1900000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5349-1156-CM25</t>
+          <t>1552-4894-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>55317.21</v>
+        <v>29468.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1557-210-CM25</t>
+          <t>5349-1156-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>18274.87</v>
+        <v>55317.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1554-1271-CM25</t>
+          <t>1557-210-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>135178.96</v>
+        <v>18274.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1552-4929-CM25</t>
+          <t>1554-1271-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1326.91</v>
+        <v>135178.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1556-147-CM25</t>
+          <t>1552-4929-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9430.5</v>
+        <v>1326.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1558-178-CM25</t>
+          <t>1556-147-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9494.4</v>
+        <v>9430.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1556-150-CM25</t>
+          <t>1558-178-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>592.7</v>
+        <v>9494.4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1373324-83-CM25</t>
+          <t>1556-150-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>165.58</v>
+        <v>592.7</v>
       </c>
     </row>
     <row r="71">
@@ -5064,7 +5064,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1557-230-CM25</t>
+          <t>1373324-83-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>10924.57</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1552-4965-CM25</t>
+          <t>1557-230-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>36091.78</v>
+        <v>10924.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5349-1500-CM25</t>
+          <t>1552-4965-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>56308.09</v>
+        <v>36091.78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1556-168-CM25</t>
+          <t>5349-1500-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>10449.19</v>
+        <v>56308.09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1552-4973-CM25</t>
+          <t>1556-168-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1272.58</v>
+        <v>10449.19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1554-1426-CM25</t>
+          <t>1552-4973-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>131542.71</v>
+        <v>1272.58</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1558-209-CM25</t>
+          <t>1554-1426-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8240.6</v>
+        <v>131542.71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1552-5033-CM25</t>
+          <t>1558-209-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>34285.36</v>
+        <v>8240.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1557-285-CM25</t>
+          <t>1552-5033-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10843.18</v>
+        <v>34285.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5349-1739-CM25</t>
+          <t>1557-285-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>53097.39</v>
+        <v>10843.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2035-91-CM25</t>
+          <t>5349-1739-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>908.49</v>
+        <v>53097.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1554-1556-CM25</t>
+          <t>2035-91-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5789,27 +5789,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>131519.93</v>
+        <v>908.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>707416-89-CM25</t>
+          <t>1554-1556-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2357.63</v>
+        <v>131519.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1556-210-CM25</t>
+          <t>707416-89-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>9197.389999999999</v>
+        <v>2357.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1552-5057-CM25</t>
+          <t>1556-210-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1276.41</v>
+        <v>9197.389999999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1558-249-CM25</t>
+          <t>1552-5057-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>8836.4</v>
+        <v>1276.41</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5349-1879-CM25</t>
+          <t>1558-249-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>52993.93</v>
+        <v>8836.4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1552-5105-CM25</t>
+          <t>5349-1879-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1291.6</v>
+        <v>52993.93</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1552-5103-CM25</t>
+          <t>1552-5105-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>34618.77</v>
+        <v>1291.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1557-319-CM25</t>
+          <t>1552-5103-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10940.56</v>
+        <v>34618.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1556-248-CM25</t>
+          <t>1557-319-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8321.15</v>
+        <v>10940.56</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1554-1672-CM25</t>
+          <t>1556-248-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>128326.35</v>
+        <v>8321.15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2609-68-CM25</t>
+          <t>1554-1672-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>329.17</v>
+        <v>128326.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1558-276-CM25</t>
+          <t>2609-68-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9109.379999999999</v>
+        <v>329.17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1552-5181-CM25</t>
+          <t>1558-276-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6649,12 +6649,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6683,13 +6683,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>36824.28</v>
+        <v>9109.379999999999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1557-365-CM25</t>
+          <t>1552-5181-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>11090.73</v>
+        <v>36824.28</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1554-1809-CM25</t>
+          <t>1557-365-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>131155.55</v>
+        <v>11090.73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5349-2314-CM25</t>
+          <t>1554-1809-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>59862.45</v>
+        <v>131155.55</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1552-5221-CM25</t>
+          <t>5349-2314-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>388.27</v>
+        <v>59862.45</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1556-286-CM25</t>
+          <t>1552-5221-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8458.780000000001</v>
+        <v>388.27</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2859-1529-CM25</t>
+          <t>1556-286-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>283.79</v>
+        <v>8458.780000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1558-302-CM25</t>
+          <t>2859-1529-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8535.93</v>
+        <v>283.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1353-59-CM25</t>
+          <t>1558-302-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.002.009-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2971.44</v>
+        <v>8535.93</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1557-418-CM25</t>
+          <t>1353-59-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.002.009-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>11163.03</v>
+        <v>2971.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1552-5275-CM25</t>
+          <t>1557-418-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7333,13 +7333,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>37338.91</v>
+        <v>11163.03</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1556-305-CM25</t>
+          <t>1552-5275-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7398,13 +7398,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9514.49</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5349-2472-CM25</t>
+          <t>1556-305-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>56850.33</v>
+        <v>9514.49</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1554-1974-CM25</t>
+          <t>5349-2472-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,13 +7528,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>133460.13</v>
+        <v>56850.33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1558-337-CM25</t>
+          <t>1554-1974-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7549,22 +7549,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,13 +7593,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>9754.059999999999</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1552-5305-CM25</t>
+          <t>1558-337-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7614,22 +7614,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7658,13 +7658,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>38172.1</v>
+        <v>9754.059999999999</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2609-87-CM25</t>
+          <t>1552-5305-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>350.04</v>
+        <v>38172.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5349-2718-CM25</t>
+          <t>2609-87-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>55794.06</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1557-455-CM25</t>
+          <t>5349-2718-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>15745.89</v>
+        <v>55794.06</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1554-2118-CM25</t>
+          <t>1557-455-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>135538.53</v>
+        <v>15745.89</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1556-6-CM26</t>
+          <t>1554-2118-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>10883.61</v>
+        <v>135538.53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1558-10-CM26</t>
+          <t>1556-6-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,13 +8048,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10939.43</v>
+        <v>10883.61</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1552-19-CM26</t>
+          <t>1558-10-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>39649.27</v>
+        <v>10939.43</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1558-12-CM26</t>
+          <t>1552-19-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8134,22 +8134,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,13 +8178,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>356.54</v>
+        <v>39649.27</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1557-13-CM26</t>
+          <t>1558-12-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8199,22 +8199,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>14183.82</v>
+        <v>356.54</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>5349-197-CM26</t>
+          <t>1557-13-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>60336.82</v>
+        <v>14183.82</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1554-167-CM26</t>
+          <t>5349-197-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,13 +8373,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>127104.35</v>
+        <v>60336.82</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1552-58-CM26</t>
+          <t>1554-167-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>28879.37</v>
+        <v>127104.35</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1556-39-CM26</t>
+          <t>1552-58-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>11426.87</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1558-62-CM26</t>
+          <t>1556-39-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>12620.2</v>
+        <v>11426.87</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1557-48-CM26</t>
+          <t>1558-62-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>20803.77</v>
+        <v>12620.2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5349-427-CM26</t>
+          <t>1557-48-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>61977.73</v>
+        <v>20803.77</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1556-65-CM26</t>
+          <t>5349-427-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>10601.97</v>
+        <v>61977.73</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>651-35-CM26</t>
+          <t>1556-65-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.815.000-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>491.54</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1554-320-CM26</t>
+          <t>651-35-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.815.000-3</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION III REGION</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>164286.67</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1558-96-CM26</t>
+          <t>1554-320-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8958,13 +8958,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>12887.39</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2859-126-CM26</t>
+          <t>1558-96-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1367.87</v>
+        <v>12887.39</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1552-114-CM26</t>
+          <t>2859-126-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9054,12 +9054,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>38300.34</v>
+        <v>1367.87</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1557-93-CM26</t>
+          <t>1552-114-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>18524.36</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>5349-614-CM26</t>
+          <t>1557-93-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>54324.56</v>
+        <v>18524.36</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1373324-29-CM26</t>
+          <t>5349-614-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>625.96</v>
+        <v>54324.56</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1373324-28-CM26</t>
+          <t>1373324-29-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2677.06</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>707416-25-CM26</t>
+          <t>1373324-28-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2358.16</v>
+        <v>2677.06</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1556-93-CM26</t>
+          <t>707416-25-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9429,12 +9429,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>10361.1</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1554-623-CM26</t>
+          <t>1556-93-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>136697.33</v>
+        <v>10361.1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1558-125-CM26</t>
+          <t>1554-623-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>13438.26</v>
+        <v>136697.33</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>707416-30-CM26</t>
+          <t>1558-125-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5607.91</v>
+        <v>13438.26</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1557-130-CM26</t>
+          <t>707416-30-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>19126.59</v>
+        <v>5607.91</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5349-860-CM26</t>
+          <t>1557-130-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>60976.5</v>
+        <v>19126.59</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1552-169-CM26</t>
+          <t>5349-860-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>39061.19</v>
+        <v>60976.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1556-116-CM26</t>
+          <t>1552-169-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>9622.07</v>
+        <v>39061.19</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1554-785-CM26</t>
+          <t>1556-116-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>138767.48</v>
+        <v>9622.07</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1373324-40-CM26</t>
+          <t>1554-785-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10019,22 +10019,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,13 +10063,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>706.89</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1373324-39-CM26</t>
+          <t>1373324-40-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2612.96</v>
+        <v>706.89</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1558-162-CM26</t>
+          <t>1373324-39-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10149,22 +10149,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12633.88</v>
+        <v>2612.96</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>707416-41-CM26</t>
+          <t>1558-162-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5706.4</v>
+        <v>12633.88</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1552-214-CM26</t>
+          <t>707416-41-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,13 +10323,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>38902.72</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1557-170-CM26</t>
+          <t>1552-214-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>19005.86</v>
+        <v>38902.72</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1556-149-CM26</t>
+          <t>1557-170-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10303.09</v>
+        <v>19005.86</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5349-1096-CM26</t>
+          <t>1556-149-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10518,13 +10518,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>57693.96</v>
+        <v>10303.09</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1554-964-CM26</t>
+          <t>5349-1096-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10534,12 +10534,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>155935.02</v>
+        <v>57693.96</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>707416-51-CM26</t>
+          <t>1554-964-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4998.24</v>
+        <v>155935.02</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1558-201-CM26</t>
+          <t>707416-51-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,18 +10713,18 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13880.7</v>
+        <v>4998.24</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2859-586-CM26</t>
+          <t>1558-201-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>666.22</v>
+        <v>13880.7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1557-226-CM26</t>
+          <t>2859-586-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>19750.96</v>
+        <v>666.22</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1552-311-CM26</t>
+          <t>1557-226-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>38227.13</v>
+        <v>19750.96</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5349-1302-CM26</t>
+          <t>1552-311-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>63704.87</v>
+        <v>38227.13</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1554-1114-CM26</t>
+          <t>5349-1302-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>152707.94</v>
+        <v>63704.87</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>707416-63-CM26</t>
+          <t>1554-1114-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>5292.22</v>
+        <v>152707.94</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1556-186-CM26</t>
+          <t>707416-63-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>9941.23</v>
+        <v>5292.22</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1558-253-CM26</t>
+          <t>1556-186-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>14189.31</v>
+        <v>9941.23</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1376-473-CM26</t>
+          <t>1558-253-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>162.25</v>
+        <v>14189.31</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2609-31-CM26</t>
+          <t>1376-473-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.902.001-6</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11344,12 +11344,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>593.83</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1079486-155-CM26</t>
+          <t>2609-31-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>60.902.001-6</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11409,12 +11409,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>305.52</v>
+        <v>593.83</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1552-386-CM26</t>
+          <t>1079486-155-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>36992.41</v>
+        <v>305.52</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1557-260-CM26</t>
+          <t>1552-386-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>18992.94</v>
+        <v>36992.41</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3281-60-CM26</t>
+          <t>1557-260-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1620.47</v>
+        <v>18992.94</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>5349-1486-CM26</t>
+          <t>3281-60-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>65433.24</v>
+        <v>1620.47</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1556-215-CM26</t>
+          <t>5349-1486-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>10338.76</v>
+        <v>65433.24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1028871-438-CM26</t>
+          <t>1556-215-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,13 +11818,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>9816.030000000001</v>
+        <v>10338.76</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1554-1309-CM26</t>
+          <t>1028871-438-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>147852.81</v>
+        <v>9816.030000000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1028871-439-CM26</t>
+          <t>1554-1309-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2502.32</v>
+        <v>147852.81</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1558-300-CM26</t>
+          <t>1028871-439-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11969,22 +11969,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.999.330-6</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12013,13 +12013,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>14110.8</v>
+        <v>2502.32</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>707416-68-CM26</t>
+          <t>1558-300-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12034,22 +12034,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -12078,13 +12078,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5259.83</v>
+        <v>14110.8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1557-296-CM26</t>
+          <t>707416-68-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>19377.64</v>
+        <v>5259.83</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1373324-62-CM26</t>
+          <t>1557-296-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>272.12</v>
+        <v>19377.64</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1079486-190-CM26</t>
+          <t>1373324-62-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>26809.85</v>
+        <v>272.12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1552-424-CM26</t>
+          <t>1079486-190-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12338,13 +12338,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>38401.19</v>
+        <v>26809.85</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5349-1763-CM26</t>
+          <t>1552-424-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>60473.35</v>
+        <v>38401.19</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>707416-73-CM26</t>
+          <t>5349-1763-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12419,27 +12419,27 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2344.84</v>
+        <v>60473.35</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1554-1513-CM26</t>
+          <t>707416-73-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12489,22 +12489,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>152580.19</v>
+        <v>2344.84</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1558-333-CM26</t>
+          <t>1554-1513-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>13971.31</v>
+        <v>152580.19</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1556-241-CM26</t>
+          <t>1558-333-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10743.56</v>
+        <v>13971.31</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>707416-83-CM26</t>
+          <t>1556-241-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5733.05</v>
+        <v>10743.56</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1552-473-CM26</t>
+          <t>707416-83-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,13 +12793,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>36764.71</v>
+        <v>5733.05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1557-337-CM26</t>
+          <t>1552-473-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12858,13 +12858,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18525.25</v>
+        <v>36764.71</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5349-1956-CM26</t>
+          <t>1557-337-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>60500.37</v>
+        <v>18525.25</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1079486-227-CM26</t>
+          <t>5349-1956-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.505.105-7</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>16093.4</v>
+        <v>60500.37</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2859-1172-CM26</t>
+          <t>1079486-227-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>60.505.105-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13034,12 +13034,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>508.21</v>
+        <v>16093.4</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2859-1174-CM26</t>
+          <t>2859-1172-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1554-1672-CM26</t>
+          <t>2859-1174-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.606.307-3</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>139198.99</v>
+        <v>508.21</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1556-274-CM26</t>
+          <t>1554-1672-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.606.305-7</t>
+          <t>61.606.307-3</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL COPIA</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>10220.51</v>
+        <v>139198.99</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1558-372-CM26</t>
+          <t>1556-274-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13269,22 +13269,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.606.306-5</t>
+          <t>61.606.305-7</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL DE CHANARAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>12739.69</v>
+        <v>10220.51</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1376-756-CM26</t>
+          <t>1558-372-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.004.010-1</t>
+          <t>61.606.306-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ATACAMA HOSPITAL FLORENCIO VARGAS DIAZ</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13359,12 +13359,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>326.27</v>
+        <v>12739.69</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>707416-97-CM26</t>
+          <t>1376-756-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.010-1</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -13443,13 +13443,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5227.79</v>
+        <v>326.27</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2859-1288-CM26</t>
+          <t>707416-97-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>489.4</v>
+        <v>5227.79</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1028871-654-CM26</t>
+          <t>2859-1288-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13529,22 +13529,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.999.330-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13573,71 +13573,136 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2416.09</v>
+        <v>489.4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
+          <t>1028871-654-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.999.330-6</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE HUASCO</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>2416.09</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
           <t>1557-378-CM26</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F204" t="inlineStr">
         <is>
           <t>61.606.309-k</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G204" t="inlineStr">
         <is>
           <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M203" s="2" t="n">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
         <v>18133.37</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/atacama.xlsx
@@ -13339,7 +13339,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
